--- a/05_Benchmark_Exemple.xlsx
+++ b/05_Benchmark_Exemple.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruccions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 3" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 4" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 23 (01 juny-07 juny)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 24 (08 juny-14 juny)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 25 (15 juny-21 juny)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 26 (22 juny-28 juny)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Setmana 27 (29 juny-05 jul)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,9 +23,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd/mm (ddd)"/>
+    <numFmt numFmtId="165" formatCode="[$-403]ddd dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,12 +56,17 @@
       <sz val="10"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
+      <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -84,17 +89,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8F1FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4FBF0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,21 +177,28 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -563,114 +575,114 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PLANTILLA DEL PLANNING DE GUÀRDIES — Telediagnòstic IDI</t>
+          <t>PLANNING DE GUÀRDIES — Telediagnòstic IDI</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Plantilla genèrica: l'app hi posa les dates i crea o treu pestanyes setmanals segons el mes. També podeu fer servir el «Planning buit» de cada mes (carpeta Plantilles mensuals).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Estructura:</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>• Una pestanya per setmana del mes (Setmana 1 fins Setmana 5).</t>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Estructura</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>• Cada pestanya té 7 columnes (dilluns a diumenge) i 3 franges horàries (8-16, 16-20, 20-08).</t>
+          <t>• Una pestanya per setmana COMPLETA, de dilluns a diumenge (nom: Setmana NN (dd mmm-dd mmm)).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>• Empleneu la fila 1 amb les dates de cada dia de la setmana abans d'omplir el planning.</t>
+          <t>• La setmana pertany al mes del seu dilluns: el planning pot acabar els primers dies del mes següent.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>• Cada pestanya té 7 columnes (dl→dg) i 3 franges: 8-16, 16-20 i 20-08. La data és a la fila 3.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Convencions de nom per cel·la:</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>• Els dies fora del període (si n'hi ha) surten en gris i no s'han d'omplir.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>• "N: Nom" — torn de Neuro fix</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>• "B: Nom" — torn de Body fix</t>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Convencions per cel·la</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>• "N i B: Nom" — un sol radiòleg cobreix Neuro i Body</t>
+          <t>• "N: Nom" — torn de Neuro fix · "B: Nom" — torn de Body fix</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>• "Grup 1: Nom" / "Grup 2: Nom" — torn repartit en dos grups</t>
+          <t>• "N i B: Nom" — un sol radiòleg cobreix Neuro i Body</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>• Festius marcats en groc; afegir prefix "FESTIU — Torn dia/nit" al nom</t>
+          <t>• "Grup 1: Nom" / "Grup 2: Nom" — torn repartit en dos grups</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>• Festius: capçalera groga; prefix "FESTIU — Torn dia/nit".</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Notes:</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>• [SUBSTITUIR — …] — torn fix que cal cobrir a mà (vacances, baixa, NO actiu…).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>• Si un dia no necessita una franja (p. ex. dissabte de tarda perquè és part del torn dia 8-20), deixar les cel·les buides o posar "(inclòs torn dia)".</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>• Els fixos del matí (8-16) NO canvien excepte si el professional té V/C; en aquest cas, substituir per l'opció documentada (sovint Bonfill o Sánchez-Montáñez).</t>
+          <t>No canvieu els noms de les pestanyes ni les files de les franges: els fluxos de Microsoft 365</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>• Empleneu només les pestanyes corresponents als dies del mes (algunes setmanes són parcials a l'inici i final).</t>
+          <t>llegeixen el fitxer automàticament (busquen les pestanyes que contenen "Setmana").</t>
         </is>
       </c>
     </row>
@@ -699,9 +711,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Setmana 1</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Setmana 23 · dl 01/06 – dg 07/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Planning de Juny 2026: dl 01/06/2026 → dg 05/07/2026 (5 setmanes)</t>
         </is>
       </c>
     </row>
@@ -711,25 +730,25 @@
           <t>Franja</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="13" t="n">
         <v>46174</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="13" t="n">
         <v>46175</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="13" t="n">
         <v>46176</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="13" t="n">
         <v>46177</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="13" t="n">
         <v>46178</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="13" t="n">
         <v>46179</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="13" t="n">
         <v>46180</v>
       </c>
     </row>
@@ -739,84 +758,84 @@
           <t>8:00-16:00</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Salvado, Anna</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Salvado, Anna</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Sarria, Carla</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Ponent, Anna</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Ponent, Anna</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>N i B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Dissabte — Torn dia 8-20:</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>Diumenge — Torn dia 8-20:</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Rivas, Elena</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Rivas, Elena</t>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Rotador-27, Cèsar</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>N i B: Sigma, Sílvia</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="11" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Rotador-28, Diana</t>
         </is>
@@ -824,7 +843,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="11" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -834,7 +853,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="11" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -844,7 +863,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="12" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -869,61 +888,61 @@
           <t>16:00-20:00</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Sarria, Carla</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>N i B: FixRota-SMontanez, Pere (fix 1r dimecres)</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Omega, Zeno</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Psi, Yolanda</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>(inclòs torn dia)</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>(inclòs torn dia)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Bonfill, Berta</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>B: FixRota-Riaza, Laia</t>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Llevant, Berta</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>B: FixRota-Mestral, Laia</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Omicron, Pere</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Rho, Roger</t>
         </is>
@@ -932,7 +951,7 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="11" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -942,7 +961,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="11" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -952,7 +971,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="11" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -962,7 +981,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="12" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -987,58 +1006,58 @@
           <t>20:00-08:00</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>N i B: Lambda, Laia</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>N i B: Mu, Marc</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>N i B: Nu, Núria</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Phi, Víctor</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Rotador-25, Aleix</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Rotador-29, Erik</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>N i B: Tau, Tomàs</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="11" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Pi, Queralt</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Rotador-26, Berta</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Rotador-30, Fina</t>
         </is>
@@ -1046,7 +1065,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="11" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -1056,7 +1075,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="11" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -1066,7 +1085,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="11" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -1076,7 +1095,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
@@ -1115,9 +1134,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Setmana 2</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Setmana 24 · dl 08/06 – dg 14/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Planning de Juny 2026: dl 01/06/2026 → dg 05/07/2026 (5 setmanes)</t>
         </is>
       </c>
     </row>
@@ -1127,25 +1153,25 @@
           <t>Franja</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="13" t="n">
         <v>46181</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="13" t="n">
         <v>46182</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="13" t="n">
         <v>46183</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="13" t="n">
         <v>46184</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="13" t="n">
         <v>46185</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="13" t="n">
         <v>46186</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="13" t="n">
         <v>46187</v>
       </c>
     </row>
@@ -1155,84 +1181,84 @@
           <t>8:00-16:00</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Salvado, Anna</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Salvado, Anna</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Sarria, Carla</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Ponent, Anna</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Ponent, Anna</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>N i B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Dissabte — Torn dia 8-20:</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>Diumenge — Torn dia 8-20:</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Rivas, Elena</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Rivas, Elena</t>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Grup 1: Special-Arce, Javi</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Grup 1: Special-Xaloc, Pau</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>N i B: Kappa, Joan</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="11" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>Grup 2: FixRota-SMontanez, Pere</t>
         </is>
@@ -1240,7 +1266,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="11" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -1250,7 +1276,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="11" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -1260,7 +1286,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="12" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -1285,61 +1311,61 @@
           <t>16:00-20:00</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Sarria, Carla</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>N i B: Novell-Nou1, Aina</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Zeta, Francesc</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Delta, David</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>(inclòs torn dia)</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>(inclòs torn dia)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Bonfill, Berta</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>B: FixRota-Riaza, Laia</t>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Llevant, Berta</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>B: FixRota-Mestral, Laia</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Alpha, Anna</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Epsilon, Elena</t>
         </is>
@@ -1348,7 +1374,7 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="11" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -1358,7 +1384,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="11" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -1368,7 +1394,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="11" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -1378,7 +1404,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="12" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -1403,58 +1429,58 @@
           <t>20:00-08:00</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>N i B: Theta, Hèctor</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>N i B: Upsilon, Ursula</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>N i B: Xi, Oriol</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Beta, Bernat</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Eta, Gabriela</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Gamma, Carla</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>N i B: Special-Lush, Olga</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="11" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Chi, Xavier</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>Grup 2: FixRota-Riaza, Laia</t>
-        </is>
-      </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Grup 2: FixRota-Mestral, Laia</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Iota, Irene</t>
         </is>
@@ -1462,7 +1488,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="11" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -1472,7 +1498,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="11" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -1482,7 +1508,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="11" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -1492,7 +1518,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
@@ -1531,9 +1557,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Setmana 3</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Setmana 25 · dl 15/06 – dg 21/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Planning de Juny 2026: dl 01/06/2026 → dg 05/07/2026 (5 setmanes)</t>
         </is>
       </c>
     </row>
@@ -1543,25 +1576,25 @@
           <t>Franja</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="13" t="n">
         <v>46188</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="13" t="n">
         <v>46189</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="13" t="n">
         <v>46190</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="13" t="n">
         <v>46191</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="13" t="n">
         <v>46192</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="13" t="n">
         <v>46193</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="13" t="n">
         <v>46194</v>
       </c>
     </row>
@@ -1571,84 +1604,84 @@
           <t>8:00-16:00</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Salvado, Anna</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Salvado, Anna</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Sarria, Carla</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Ponent, Anna</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Ponent, Anna</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>N i B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Dissabte — Torn dia 8-20:</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>Diumenge — Torn dia 8-20:</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Rivas, Elena</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Rivas, Elena</t>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Rotador-27, Cèsar</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>N i B: Sigma, Sílvia</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="11" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Rotador-28, Diana</t>
         </is>
@@ -1656,7 +1689,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="11" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -1666,7 +1699,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="11" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -1676,7 +1709,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="12" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -1701,61 +1734,61 @@
           <t>16:00-20:00</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Sarria, Carla</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>N i B: Novell-Nou2, Bernat</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Omega, Zeno</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Psi, Yolanda</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>(inclòs torn dia)</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>(inclòs torn dia)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Bonfill, Berta</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>B: FixRota-Riaza, Laia</t>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Llevant, Berta</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>B: FixRota-Mestral, Laia</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Omicron, Pere</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Rho, Roger</t>
         </is>
@@ -1764,7 +1797,7 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="11" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -1774,7 +1807,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="11" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -1784,7 +1817,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="11" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -1794,7 +1827,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="12" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -1819,58 +1852,58 @@
           <t>20:00-08:00</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>N i B: Lambda, Laia</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>N i B: Mu, Marc</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>N i B: Nu, Núria</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Phi, Víctor</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Rotador-25, Aleix</t>
         </is>
       </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Rotador-29, Erik</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>N i B: Tau, Tomàs</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="11" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Pi, Queralt</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Rotador-26, Berta</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Rotador-30, Fina</t>
         </is>
@@ -1878,7 +1911,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="11" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -1888,7 +1921,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="11" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -1898,7 +1931,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="11" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -1908,7 +1941,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
@@ -1947,9 +1980,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Setmana 4</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Setmana 26 · dl 22/06 – dg 28/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Planning de Juny 2026: dl 01/06/2026 → dg 05/07/2026 (5 setmanes)</t>
         </is>
       </c>
     </row>
@@ -1959,25 +1999,25 @@
           <t>Franja</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="13" t="n">
         <v>46195</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="13" t="n">
         <v>46196</v>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="17" t="n">
         <v>46197</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="13" t="n">
         <v>46198</v>
       </c>
-      <c r="F3" s="8" t="n">
+      <c r="F3" s="13" t="n">
         <v>46199</v>
       </c>
-      <c r="G3" s="8" t="n">
+      <c r="G3" s="13" t="n">
         <v>46200</v>
       </c>
-      <c r="H3" s="8" t="n">
+      <c r="H3" s="13" t="n">
         <v>46201</v>
       </c>
     </row>
@@ -1987,84 +2027,84 @@
           <t>8:00-16:00</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Salvado, Anna</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Ponent, Anna</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>FESTIU — Torn dia 8-20:</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Sarria, Carla</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>N i B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>Dissabte — Torn dia 8-20:</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>Diumenge — Torn dia 8-20:</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Rivas, Elena</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>N i B: Xi, Oriol</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Rivas, Elena</t>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
         </is>
       </c>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Grup 1: Special-Arce, Javi</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Grup 1: Special-Xaloc, Pau</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>N i B: Lambda, Laia</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="11" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>Grup 2: FixRota-SMontanez, Pere</t>
         </is>
@@ -2072,7 +2112,7 @@
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="11" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -2082,7 +2122,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="11" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -2092,7 +2132,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="12" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -2117,61 +2157,61 @@
           <t>16:00-20:00</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Sarria, Carla</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>(inclòs torn dia)</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Alpha, Anna</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Epsilon, Elena</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>(inclòs torn dia)</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>(inclòs torn dia)</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Bonfill, Berta</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>B: FixRota-Riaza, Laia</t>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Llevant, Berta</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>B: FixRota-Mestral, Laia</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Beta, Bernat</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Eta, Gabriela</t>
         </is>
@@ -2180,7 +2220,7 @@
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="11" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -2190,7 +2230,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="11" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -2200,7 +2240,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="11" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -2210,7 +2250,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="12" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -2235,62 +2275,62 @@
           <t>20:00-08:00</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>N i B: Theta, Hèctor</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>N i B: Upsilon, Ursula</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>FESTIU — Torn nit 20-08:</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Chi, Xavier</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>Grup 1: FixRota-Riaza, Laia</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Grup 1: FixRota-Mestral, Laia</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
         <is>
           <t>Grup 1: Iota, Irene</t>
         </is>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>N i B: Special-Lush, Olga</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="11" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>N i B: Zeta, Francesc</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Delta, David</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Gamma, Carla</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Grup 2: Kappa, Joan</t>
         </is>
@@ -2298,7 +2338,7 @@
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="11" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -2308,7 +2348,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="11" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -2318,7 +2358,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="11" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -2328,7 +2368,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
@@ -2367,9 +2407,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Setmana 5</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Setmana 27 · dl 29/06 – dg 05/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Planning de Juny 2026: dl 01/06/2026 → dg 05/07/2026 (5 setmanes)</t>
         </is>
       </c>
     </row>
@@ -2379,41 +2426,26 @@
           <t>Franja</t>
         </is>
       </c>
-      <c r="B3" s="8" t="n">
+      <c r="B3" s="13" t="n">
         <v>46202</v>
       </c>
-      <c r="C3" s="8" t="n">
+      <c r="C3" s="13" t="n">
         <v>46203</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Dimecres
-(data)</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>Dijous
-(data)</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Divendres
-(data)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>Dissabte
-(data)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Diumenge
-(data)</t>
-        </is>
+      <c r="D3" s="13" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E3" s="13" t="n">
+        <v>46205</v>
+      </c>
+      <c r="F3" s="13" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G3" s="13" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H3" s="13" t="n">
+        <v>46208</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -2422,52 +2454,92 @@
           <t>8:00-16:00</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Salvado, Anna</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Ponent, Anna</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Ponent, Anna</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>N i B: FixRota-SMontanez, Pere</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Dissabte — Torn dia 8-20:</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Diumenge — Torn dia 8-20:</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>B: FixRota-SMontanez, Pere</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Rivas, Elena</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>B: FixRota-SMontanez, Pere</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Garbí, Elena</t>
+        </is>
+      </c>
       <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>Grup 1: Rotador-28, Diana</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>N i B: Tau, Tomàs</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="11" t="n"/>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>Grup 2: Rotador-29, Erik</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="11" t="n"/>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
@@ -2477,7 +2549,7 @@
       <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="11" t="n"/>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
@@ -2487,7 +2559,7 @@
       <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="12" t="n"/>
+      <c r="A9" s="10" t="n"/>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
@@ -2512,42 +2584,70 @@
           <t>16:00-20:00</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Sarria, Carla</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>N: Fix-Siurana, Dora</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Migjorn, Carla</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>N: Fix-Tramuntana, Dora</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>N i B: FixRota-SMontanez, Pere (fix 1r dimecres)</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Grup 1: Omicron, Pere</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Grup 1: Rho, Roger</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>(inclòs torn dia)</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>(inclòs torn dia)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>B: Fix-Bonfill, Berta</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>B: FixRota-Riaza, Laia</t>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>B: Fix-Llevant, Berta</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>B: FixRota-Mestral, Laia</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Grup 2: Phi, Víctor</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Grup 2: Rotador-25, Aleix</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="n"/>
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="11" t="n"/>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
@@ -2557,7 +2657,7 @@
       <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="11" t="n"/>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
@@ -2567,7 +2667,7 @@
       <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="11" t="n"/>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
@@ -2577,7 +2677,7 @@
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="12" t="n"/>
+      <c r="A16" s="10" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
@@ -2602,34 +2702,66 @@
           <t>20:00-08:00</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>N i B: Mu, Marc</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>N i B: Nu, Núria</t>
         </is>
       </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>N i B: Omega, Zeno</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>Grup 1: Pi, Queralt</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Grup 1: Rotador-26, Berta</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Grup 1: Rotador-30, Fina</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>N i B: Special-Lush, Olga</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="11" t="n"/>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>Grup 2: Psi, Yolanda</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Grup 2: Rotador-27, Cèsar</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Grup 2: Sigma, Sílvia</t>
+        </is>
+      </c>
       <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="11" t="n"/>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
@@ -2639,7 +2771,7 @@
       <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="11" t="n"/>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
@@ -2649,7 +2781,7 @@
       <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="11" t="n"/>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
@@ -2659,7 +2791,7 @@
       <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="12" t="n"/>
+      <c r="A23" s="10" t="n"/>
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
